--- a/output/yearly_benthic_cover_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_54_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.47384924035369</v>
+        <v>45.69891309445059</v>
       </c>
       <c r="M2" t="n">
-        <v>99.95945651987523</v>
+        <v>99.15673678799814</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0207847863484</v>
+        <v>88.08434313272134</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89541116646026</v>
+        <v>45.95387812833282</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228739115439597</v>
+        <v>2.228857738050413</v>
       </c>
       <c r="E3" t="n">
-        <v>5.687102762400534</v>
+        <v>5.7238581475468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429130384798657</v>
+        <v>0.7429525793501379</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96161928612718</v>
+        <v>33.98127189328609</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17399977007381</v>
+        <v>34.17581865010634</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583204323328268</v>
+        <v>6.588130503443213</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64320649049916</v>
+        <v>4.643453620938361</v>
       </c>
       <c r="K3" t="n">
-        <v>11.97921521365157</v>
+        <v>11.91565686727863</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88907124505306</v>
+        <v>48.89399839134375</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636976251649</v>
+        <v>106.7635333869552</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.15444591939163</v>
+        <v>87.23646043173829</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66836926928596</v>
+        <v>42.74407578272861</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187221345080231</v>
+        <v>2.188382194734129</v>
       </c>
       <c r="E4" t="n">
-        <v>6.497417740489056</v>
+        <v>6.536855876523063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444750903770848</v>
+        <v>0.7445144129668917</v>
       </c>
       <c r="G4" t="n">
-        <v>33.32896977556501</v>
+        <v>33.36417982007812</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2458541573459</v>
+        <v>34.24766299647701</v>
       </c>
       <c r="I4" t="n">
-        <v>5.497538495677574</v>
+        <v>5.501650049916008</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652969314856779</v>
+        <v>4.653215081043072</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84555408060838</v>
+        <v>12.76353956826169</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30320986334653</v>
+        <v>44.30938102391404</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81713321324087</v>
+        <v>99.81699637490435</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.13284536513729</v>
+        <v>86.08103381611541</v>
       </c>
       <c r="C5" t="n">
-        <v>42.50003041054558</v>
+        <v>42.44262375116763</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137827258821498</v>
+        <v>2.132092556862522</v>
       </c>
       <c r="E5" t="n">
-        <v>7.115589507621664</v>
+        <v>7.134191706456877</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457973533052876</v>
+        <v>0.7458385343686592</v>
       </c>
       <c r="G5" t="n">
-        <v>32.57630063592263</v>
+        <v>32.5059853033824</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30667825204323</v>
+        <v>34.30857258095832</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589418899264925</v>
+        <v>4.592862294282509</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661233458158047</v>
+        <v>4.661490839804119</v>
       </c>
       <c r="K5" t="n">
-        <v>13.86715463486272</v>
+        <v>13.9189661838846</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48010555193399</v>
+        <v>43.48558645245009</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84729059734229</v>
+        <v>99.84717638750232</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.88817170396486</v>
+        <v>84.72714398320548</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96826038606321</v>
+        <v>41.80211580903309</v>
       </c>
       <c r="D6" t="n">
-        <v>2.077334365475599</v>
+        <v>2.066099924888808</v>
       </c>
       <c r="E6" t="n">
-        <v>7.552621679364616</v>
+        <v>7.552233375332738</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469190658177211</v>
+        <v>0.7469632885442016</v>
       </c>
       <c r="G6" t="n">
-        <v>31.65450741252668</v>
+        <v>31.49985847358578</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35827702761517</v>
+        <v>34.36031127303327</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830267991804327</v>
+        <v>3.833157094419419</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668244161360755</v>
+        <v>4.668520553401259</v>
       </c>
       <c r="K6" t="n">
-        <v>15.11182829603515</v>
+        <v>15.27285601679453</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79242745958871</v>
+        <v>42.79744866599786</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87251614168706</v>
+        <v>99.87242049182548</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.37195827682116</v>
+        <v>83.25293132709251</v>
       </c>
       <c r="C7" t="n">
-        <v>41.04715076156929</v>
+        <v>40.92332533601905</v>
       </c>
       <c r="D7" t="n">
-        <v>2.003599094416441</v>
+        <v>1.994574904983143</v>
       </c>
       <c r="E7" t="n">
-        <v>7.817201755783549</v>
+        <v>7.82385203033546</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747873475394437</v>
+        <v>0.7479198428680911</v>
       </c>
       <c r="G7" t="n">
-        <v>30.530926287072</v>
+        <v>30.40938459223655</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4021798681441</v>
+        <v>34.40431277193218</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195968574795405</v>
+        <v>3.198388166811529</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67420922121523</v>
+        <v>4.674499017925569</v>
       </c>
       <c r="K7" t="n">
-        <v>16.62804172317885</v>
+        <v>16.74706867290747</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21841118214619</v>
+        <v>42.22312940511738</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89360366689434</v>
+        <v>99.89352341404391</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.20841975926436</v>
+        <v>88.18988551090884</v>
       </c>
       <c r="C8" t="n">
-        <v>43.29748761095284</v>
+        <v>43.27379689837924</v>
       </c>
       <c r="D8" t="n">
-        <v>2.007883332409443</v>
+        <v>1.998842748090532</v>
       </c>
       <c r="E8" t="n">
-        <v>9.616664024351412</v>
+        <v>9.69041836759658</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494726316159447</v>
+        <v>0.7495201861484009</v>
       </c>
       <c r="G8" t="n">
-        <v>31.01604938803067</v>
+        <v>30.92760965022499</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47574105433345</v>
+        <v>34.47792856282643</v>
       </c>
       <c r="I8" t="n">
-        <v>5.658405380923779</v>
+        <v>5.661064832594398</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684203947599653</v>
+        <v>4.684501163427504</v>
       </c>
       <c r="K8" t="n">
-        <v>11.79158024073563</v>
+        <v>11.81011448909116</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72272108189372</v>
+        <v>44.72778936018535</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81178893358219</v>
+        <v>99.81170074765575</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.38960395646178</v>
+        <v>86.19567119170571</v>
       </c>
       <c r="C9" t="n">
-        <v>42.35714320984431</v>
+        <v>42.15843563738437</v>
       </c>
       <c r="D9" t="n">
-        <v>1.925741666133676</v>
+        <v>1.908791197905666</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01057242261724</v>
+        <v>10.04154320265278</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508387134970981</v>
+        <v>0.7508900788070682</v>
       </c>
       <c r="G9" t="n">
-        <v>29.74719579633962</v>
+        <v>29.53426382791069</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53858082086651</v>
+        <v>34.54094362512513</v>
       </c>
       <c r="I9" t="n">
-        <v>4.72393257765078</v>
+        <v>4.726176266760221</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692741959356861</v>
+        <v>4.693062992544175</v>
       </c>
       <c r="K9" t="n">
-        <v>13.61039604353821</v>
+        <v>13.80432880829429</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87528281936959</v>
+        <v>43.87998375341594</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84282207275211</v>
+        <v>99.84274819909459</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.35108007173355</v>
+        <v>83.96164533523665</v>
       </c>
       <c r="C10" t="n">
-        <v>41.05192646075531</v>
+        <v>40.65787582119051</v>
       </c>
       <c r="D10" t="n">
-        <v>1.834417349692632</v>
+        <v>1.808827387596779</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1929657241386</v>
+        <v>10.17310674809873</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520085719917255</v>
+        <v>0.7520660114209097</v>
       </c>
       <c r="G10" t="n">
-        <v>28.33649654736254</v>
+        <v>27.98754800580021</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59239431161937</v>
+        <v>34.59503652536184</v>
       </c>
       <c r="I10" t="n">
-        <v>3.942743991980381</v>
+        <v>3.944648085577497</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700053574948283</v>
+        <v>4.700412571380685</v>
       </c>
       <c r="K10" t="n">
-        <v>15.64891992826647</v>
+        <v>16.03835466476334</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16793326159902</v>
+        <v>43.17248683996949</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86877965062079</v>
+        <v>99.86871732592334</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.16654162743367</v>
+        <v>81.51015619065925</v>
       </c>
       <c r="C11" t="n">
-        <v>39.47895308110514</v>
+        <v>38.81792679800276</v>
       </c>
       <c r="D11" t="n">
-        <v>1.73745249402636</v>
+        <v>1.700170254162501</v>
       </c>
       <c r="E11" t="n">
-        <v>10.20251335685894</v>
+        <v>10.11060859608435</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530122701398122</v>
+        <v>0.7530783696376004</v>
       </c>
       <c r="G11" t="n">
-        <v>26.83866711489278</v>
+        <v>26.30632250080339</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63856442643136</v>
+        <v>34.64160500332962</v>
       </c>
       <c r="I11" t="n">
-        <v>3.290005276710595</v>
+        <v>3.291631656406784</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706326688373824</v>
+        <v>4.706739810235002</v>
       </c>
       <c r="K11" t="n">
-        <v>17.83345837256633</v>
+        <v>18.48984380934075</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57806787988464</v>
+        <v>42.58265583472377</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8904793335561</v>
+        <v>99.89042644206728</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.96616968086217</v>
+        <v>79.01747005091789</v>
       </c>
       <c r="C12" t="n">
-        <v>37.78821846666729</v>
+        <v>36.83466464433633</v>
       </c>
       <c r="D12" t="n">
-        <v>1.640741314641147</v>
+        <v>1.590827613283254</v>
       </c>
       <c r="E12" t="n">
-        <v>10.09208259981184</v>
+        <v>9.918068142571549</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538738320058321</v>
+        <v>0.7539507956638327</v>
       </c>
       <c r="G12" t="n">
-        <v>25.34475625474985</v>
+        <v>24.61449030516489</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67819627226827</v>
+        <v>34.6817366005363</v>
       </c>
       <c r="I12" t="n">
-        <v>2.744807957348773</v>
+        <v>2.746204120799121</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711711450036449</v>
+        <v>4.712192472898954</v>
       </c>
       <c r="K12" t="n">
-        <v>20.03383031913785</v>
+        <v>20.9825299490821</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08656217873067</v>
+        <v>42.0913711939036</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90861096453581</v>
+        <v>99.90856578732203</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.71995057059247</v>
+        <v>76.46759601349432</v>
       </c>
       <c r="C13" t="n">
-        <v>35.96645821834854</v>
+        <v>34.70888005825982</v>
       </c>
       <c r="D13" t="n">
-        <v>1.542856151078254</v>
+        <v>1.480010876253675</v>
       </c>
       <c r="E13" t="n">
-        <v>9.87159563394712</v>
+        <v>9.608975594270547</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546141219941422</v>
+        <v>0.7547036818786796</v>
       </c>
       <c r="G13" t="n">
-        <v>23.83271069990231</v>
+        <v>22.89984977687095</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71224961173053</v>
+        <v>34.71636936641925</v>
       </c>
       <c r="I13" t="n">
-        <v>2.289586089476725</v>
+        <v>2.290788706059457</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716338262463387</v>
+        <v>4.716898011741747</v>
       </c>
       <c r="K13" t="n">
-        <v>22.28004942940753</v>
+        <v>23.53240398650568</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67724768676203</v>
+        <v>41.68243250743452</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92375533451811</v>
+        <v>99.92371655220002</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.14841686039678</v>
+        <v>83.437611887568</v>
       </c>
       <c r="C14" t="n">
-        <v>39.87858705216509</v>
+        <v>39.07772620972062</v>
       </c>
       <c r="D14" t="n">
-        <v>1.544725899715443</v>
+        <v>1.481730354994126</v>
       </c>
       <c r="E14" t="n">
-        <v>12.07925648489299</v>
+        <v>12.03209502822004</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555286199045377</v>
+        <v>0.7555804976893951</v>
       </c>
       <c r="G14" t="n">
-        <v>25.54740390617715</v>
+        <v>24.8537208866919</v>
       </c>
       <c r="H14" t="n">
-        <v>36.44012745808956</v>
+        <v>36.68396892550118</v>
       </c>
       <c r="I14" t="n">
-        <v>3.059320617213741</v>
+        <v>2.908138083912639</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722053874403358</v>
+        <v>4.722378110558718</v>
       </c>
       <c r="K14" t="n">
-        <v>15.85158313960323</v>
+        <v>16.56238811243201</v>
       </c>
       <c r="L14" t="n">
-        <v>44.16797588853287</v>
+        <v>44.26306023365569</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89814608030119</v>
+        <v>99.90317455580831</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.52280795334251</v>
+        <v>82.61914846149151</v>
       </c>
       <c r="C15" t="n">
-        <v>39.72621164491557</v>
+        <v>38.70857140872907</v>
       </c>
       <c r="D15" t="n">
-        <v>1.521603146587868</v>
+        <v>1.451541072769157</v>
       </c>
       <c r="E15" t="n">
-        <v>12.32378244677235</v>
+        <v>12.19125237769215</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562981231022147</v>
+        <v>0.7563199963494672</v>
       </c>
       <c r="G15" t="n">
-        <v>25.16498893295647</v>
+        <v>24.34734265690129</v>
       </c>
       <c r="H15" t="n">
-        <v>36.47724159759932</v>
+        <v>36.71987210980714</v>
       </c>
       <c r="I15" t="n">
-        <v>2.552030436935453</v>
+        <v>2.425820270788142</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72686326938884</v>
+        <v>4.726999977184168</v>
       </c>
       <c r="K15" t="n">
-        <v>16.47719204665747</v>
+        <v>17.38085153850849</v>
       </c>
       <c r="L15" t="n">
-        <v>43.71161518017103</v>
+        <v>43.82979543932042</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91501887174408</v>
+        <v>99.91921838655799</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.21666296111269</v>
+        <v>80.14799131513185</v>
       </c>
       <c r="C16" t="n">
-        <v>37.81497632898565</v>
+        <v>36.61221843940633</v>
       </c>
       <c r="D16" t="n">
-        <v>1.432902459813301</v>
+        <v>1.358264144599618</v>
       </c>
       <c r="E16" t="n">
-        <v>11.96013533581889</v>
+        <v>11.74503793399291</v>
       </c>
       <c r="F16" t="n">
-        <v>0.75695883247636</v>
+        <v>0.756956402464882</v>
       </c>
       <c r="G16" t="n">
-        <v>23.69801523088895</v>
+        <v>22.78276734123738</v>
       </c>
       <c r="H16" t="n">
-        <v>36.50910846957784</v>
+        <v>36.75077007796973</v>
       </c>
       <c r="I16" t="n">
-        <v>2.128549929560111</v>
+        <v>2.023217899461831</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730992702977248</v>
+        <v>4.730977515405511</v>
       </c>
       <c r="K16" t="n">
-        <v>18.78333703888731</v>
+        <v>19.85200868486814</v>
       </c>
       <c r="L16" t="n">
-        <v>43.3307968977677</v>
+        <v>43.46838897931477</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92911026564066</v>
+        <v>99.93261610358923</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.85368798803607</v>
+        <v>81.90344456761855</v>
       </c>
       <c r="C17" t="n">
-        <v>39.00594280014511</v>
+        <v>37.89104679722961</v>
       </c>
       <c r="D17" t="n">
-        <v>1.434134561163764</v>
+        <v>1.3593744967042</v>
       </c>
       <c r="E17" t="n">
-        <v>12.72799000351542</v>
+        <v>12.54654567413055</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576097141838699</v>
+        <v>0.7575751982550055</v>
       </c>
       <c r="G17" t="n">
-        <v>24.11974833026974</v>
+        <v>23.25852655453439</v>
       </c>
       <c r="H17" t="n">
-        <v>36.94185736781654</v>
+        <v>37.23794783698717</v>
       </c>
       <c r="I17" t="n">
-        <v>2.137287297437553</v>
+        <v>2.00862981791345</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735060713649185</v>
+        <v>4.734844989093783</v>
       </c>
       <c r="K17" t="n">
-        <v>17.14631201196392</v>
+        <v>18.09655543238146</v>
       </c>
       <c r="L17" t="n">
-        <v>43.77656348456598</v>
+        <v>43.94549813215923</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92881829667503</v>
+        <v>99.9331003617703</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.67067379287288</v>
+        <v>79.49863393111188</v>
       </c>
       <c r="C18" t="n">
-        <v>37.15331387194702</v>
+        <v>35.79618765071658</v>
       </c>
       <c r="D18" t="n">
-        <v>1.353349386951148</v>
+        <v>1.272306011235046</v>
       </c>
       <c r="E18" t="n">
-        <v>12.30808308444307</v>
+        <v>12.02210665475387</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581676830777081</v>
+        <v>0.7581072677971598</v>
       </c>
       <c r="G18" t="n">
-        <v>22.76107661034123</v>
+        <v>21.76880853624198</v>
       </c>
       <c r="H18" t="n">
-        <v>36.96906452594288</v>
+        <v>37.26410125106676</v>
       </c>
       <c r="I18" t="n">
-        <v>1.782384482881175</v>
+        <v>1.675033786284826</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738548019235674</v>
+        <v>4.738170423732247</v>
       </c>
       <c r="K18" t="n">
-        <v>19.32932620712714</v>
+        <v>20.5013660688881</v>
       </c>
       <c r="L18" t="n">
-        <v>43.45799082933035</v>
+        <v>43.64665100767549</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9406309084045</v>
+        <v>99.94420472728018</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.84962837033422</v>
+        <v>78.54157718162689</v>
       </c>
       <c r="C19" t="n">
-        <v>36.60718474267468</v>
+        <v>35.09403250892106</v>
       </c>
       <c r="D19" t="n">
-        <v>1.323662578001021</v>
+        <v>1.238191700945056</v>
       </c>
       <c r="E19" t="n">
-        <v>12.28580235846828</v>
+        <v>11.93300520172494</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586380758376482</v>
+        <v>0.7585575420431908</v>
       </c>
       <c r="G19" t="n">
-        <v>22.26179406043545</v>
+        <v>21.18512199975548</v>
       </c>
       <c r="H19" t="n">
-        <v>36.99200137841352</v>
+        <v>37.28623408873708</v>
       </c>
       <c r="I19" t="n">
-        <v>1.486241945192996</v>
+        <v>1.399482010651199</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7414879739853</v>
+        <v>4.740984637769941</v>
       </c>
       <c r="K19" t="n">
-        <v>20.15037162966578</v>
+        <v>21.45842281837311</v>
       </c>
       <c r="L19" t="n">
-        <v>43.19293294757953</v>
+        <v>43.40092296309593</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95048931992</v>
+        <v>99.95337829039009</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.45334912137747</v>
+        <v>75.96435201330043</v>
       </c>
       <c r="C20" t="n">
-        <v>34.44004031617357</v>
+        <v>32.73202377762154</v>
       </c>
       <c r="D20" t="n">
-        <v>1.235897760441663</v>
+        <v>1.145895666680294</v>
       </c>
       <c r="E20" t="n">
-        <v>11.67773065674854</v>
+        <v>11.23797921118843</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590426638387502</v>
+        <v>0.7589459300567866</v>
       </c>
       <c r="G20" t="n">
-        <v>20.78573639534022</v>
+        <v>19.60596204859427</v>
       </c>
       <c r="H20" t="n">
-        <v>37.01172952068733</v>
+        <v>37.30532496265178</v>
       </c>
       <c r="I20" t="n">
-        <v>1.239195475328783</v>
+        <v>1.166832131273943</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744016648992187</v>
+        <v>4.743412062854914</v>
       </c>
       <c r="K20" t="n">
-        <v>22.54665087862253</v>
+        <v>24.03564798669958</v>
       </c>
       <c r="L20" t="n">
-        <v>42.97202430672632</v>
+        <v>43.19345373538302</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95871550152242</v>
+        <v>99.96112549970414</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.88568314571749</v>
+        <v>82.00397553253342</v>
       </c>
       <c r="C21" t="n">
-        <v>37.72850437940553</v>
+        <v>36.52039566175605</v>
       </c>
       <c r="D21" t="n">
-        <v>1.236822603817476</v>
+        <v>1.146655668951619</v>
       </c>
       <c r="E21" t="n">
-        <v>13.47780321431963</v>
+        <v>13.26846032621849</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596106684116853</v>
+        <v>0.759449292315174</v>
       </c>
       <c r="G21" t="n">
-        <v>22.28250077624847</v>
+        <v>21.37005211143211</v>
       </c>
       <c r="H21" t="n">
-        <v>38.52063608903074</v>
+        <v>39.08115392668877</v>
       </c>
       <c r="I21" t="n">
-        <v>1.860743116316463</v>
+        <v>1.63164612995742</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747566677573032</v>
+        <v>4.746558076969835</v>
       </c>
       <c r="K21" t="n">
-        <v>17.11431685428252</v>
+        <v>17.99602446746658</v>
       </c>
       <c r="L21" t="n">
-        <v>45.09520037525531</v>
+        <v>45.42922771489483</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93802160894336</v>
+        <v>99.94564784411746</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_54_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.69891309445059</v>
+        <v>45.27959449086548</v>
       </c>
       <c r="M2" t="n">
-        <v>99.15673678799814</v>
+        <v>100.0938855455669</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08434313272134</v>
+        <v>87.96871288811518</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95387812833282</v>
+        <v>45.90896296633276</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228857738050413</v>
+        <v>2.228595177605697</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7238581475468</v>
+        <v>5.691848593596602</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429525793501379</v>
+        <v>0.7428650592018989</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98127189328609</v>
+        <v>33.96689678444901</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17581865010634</v>
+        <v>34.17179272328735</v>
       </c>
       <c r="I3" t="n">
-        <v>6.588130503443213</v>
+        <v>6.523807929962755</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643453620938361</v>
+        <v>4.642906620011868</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91565686727863</v>
+        <v>12.03128711188482</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89399839134375</v>
+        <v>48.8255644404346</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7635333869552</v>
+        <v>106.7658145186522</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.23646043173829</v>
+        <v>86.95403958337575</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74407578272861</v>
+        <v>42.52161674483083</v>
       </c>
       <c r="D4" t="n">
-        <v>2.188382194734129</v>
+        <v>2.179151456348896</v>
       </c>
       <c r="E4" t="n">
-        <v>6.536855876523063</v>
+        <v>6.473545670137641</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445144129668917</v>
+        <v>0.7444164630777247</v>
       </c>
       <c r="G4" t="n">
-        <v>33.36417982007812</v>
+        <v>33.21330555646603</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24766299647701</v>
+        <v>34.24315730157533</v>
       </c>
       <c r="I4" t="n">
-        <v>5.501650049916008</v>
+        <v>5.447860241534332</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653215081043072</v>
+        <v>4.652602894235779</v>
       </c>
       <c r="K4" t="n">
-        <v>12.76353956826169</v>
+        <v>13.04596041662425</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30938102391404</v>
+        <v>44.25120595160151</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81699637490435</v>
+        <v>99.8187831130566</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.08103381611541</v>
+        <v>85.66490875164759</v>
       </c>
       <c r="C5" t="n">
-        <v>42.44262375116763</v>
+        <v>42.07793557007077</v>
       </c>
       <c r="D5" t="n">
-        <v>2.132092556862522</v>
+        <v>2.115788995741986</v>
       </c>
       <c r="E5" t="n">
-        <v>7.134191706456877</v>
+        <v>7.043302799897259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458385343686592</v>
+        <v>0.74573382267966</v>
       </c>
       <c r="G5" t="n">
-        <v>32.5059853033824</v>
+        <v>32.24757334046264</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30857258095832</v>
+        <v>34.30375584326436</v>
       </c>
       <c r="I5" t="n">
-        <v>4.592862294282509</v>
+        <v>4.547917557853802</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661490839804119</v>
+        <v>4.660836391747875</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9189661838846</v>
+        <v>14.33509124835243</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48558645245009</v>
+        <v>43.43564373042305</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84717638750232</v>
+        <v>99.84867054884626</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.72714398320548</v>
+        <v>84.17649388579494</v>
       </c>
       <c r="C6" t="n">
-        <v>41.80211580903309</v>
+        <v>41.29563930929751</v>
       </c>
       <c r="D6" t="n">
-        <v>2.066099924888808</v>
+        <v>2.042800097690808</v>
       </c>
       <c r="E6" t="n">
-        <v>7.552233375332738</v>
+        <v>7.432932856885212</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469632885442016</v>
+        <v>0.7468546929865996</v>
       </c>
       <c r="G6" t="n">
-        <v>31.49985847358578</v>
+        <v>31.13512080021322</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36031127303327</v>
+        <v>34.35531587738357</v>
       </c>
       <c r="I6" t="n">
-        <v>3.833157094419419</v>
+        <v>3.795627729469295</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668520553401259</v>
+        <v>4.667841831166247</v>
       </c>
       <c r="K6" t="n">
-        <v>15.27285601679453</v>
+        <v>15.82350611420505</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79744866599786</v>
+        <v>42.75452353322373</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87242049182548</v>
+        <v>99.87366895672629</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.25293132709251</v>
+        <v>82.39209056447311</v>
       </c>
       <c r="C7" t="n">
-        <v>40.92332533601905</v>
+        <v>40.10047564443585</v>
       </c>
       <c r="D7" t="n">
-        <v>1.994574904983143</v>
+        <v>1.955543789262939</v>
       </c>
       <c r="E7" t="n">
-        <v>7.82385203033546</v>
+        <v>7.643288017954902</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479198428680911</v>
+        <v>0.7478116398168456</v>
       </c>
       <c r="G7" t="n">
-        <v>30.40938459223655</v>
+        <v>29.80521303951095</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40431277193218</v>
+        <v>34.39933543157489</v>
       </c>
       <c r="I7" t="n">
-        <v>3.198388166811529</v>
+        <v>3.167075897497298</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674499017925569</v>
+        <v>4.673822748855285</v>
       </c>
       <c r="K7" t="n">
-        <v>16.74706867290747</v>
+        <v>17.60790943552689</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22312940511738</v>
+        <v>42.1861808164409</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89352341404391</v>
+        <v>99.89456589640363</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.18988551090884</v>
+        <v>87.4180395505264</v>
       </c>
       <c r="C8" t="n">
-        <v>43.27379689837924</v>
+        <v>42.47365304477685</v>
       </c>
       <c r="D8" t="n">
-        <v>1.998842748090532</v>
+        <v>1.959789747270413</v>
       </c>
       <c r="E8" t="n">
-        <v>9.69041836759658</v>
+        <v>9.527451407844318</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495201861484009</v>
+        <v>0.7494353195511457</v>
       </c>
       <c r="G8" t="n">
-        <v>30.92760965022499</v>
+        <v>30.32919713210622</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47792856282643</v>
+        <v>34.47402469935269</v>
       </c>
       <c r="I8" t="n">
-        <v>5.661064832594398</v>
+        <v>5.694170497206941</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684501163427504</v>
+        <v>4.68397074719466</v>
       </c>
       <c r="K8" t="n">
-        <v>11.81011448909116</v>
+        <v>12.5819604494736</v>
       </c>
       <c r="L8" t="n">
-        <v>44.72778936018535</v>
+        <v>44.75499204364247</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81170074765575</v>
+        <v>99.81060553789293</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.19567119170571</v>
+        <v>85.28181506397294</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15843563738437</v>
+        <v>41.22050613371963</v>
       </c>
       <c r="D9" t="n">
-        <v>1.908791197905666</v>
+        <v>1.863127926977934</v>
       </c>
       <c r="E9" t="n">
-        <v>10.04154320265278</v>
+        <v>9.84985978018233</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508900788070682</v>
+        <v>0.7508278731429323</v>
       </c>
       <c r="G9" t="n">
-        <v>29.53426382791069</v>
+        <v>28.83328390627062</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54094362512513</v>
+        <v>34.53808216457487</v>
       </c>
       <c r="I9" t="n">
-        <v>4.726176266760221</v>
+        <v>4.753959205680934</v>
       </c>
       <c r="J9" t="n">
-        <v>4.693062992544175</v>
+        <v>4.692674207143327</v>
       </c>
       <c r="K9" t="n">
-        <v>13.80432880829429</v>
+        <v>14.71818493602703</v>
       </c>
       <c r="L9" t="n">
-        <v>43.87998375341594</v>
+        <v>43.90313752755314</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84274819909459</v>
+        <v>99.84182859729981</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.96164533523665</v>
+        <v>82.97716536676143</v>
       </c>
       <c r="C10" t="n">
-        <v>40.65787582119051</v>
+        <v>39.6527219012624</v>
       </c>
       <c r="D10" t="n">
-        <v>1.808827387596779</v>
+        <v>1.760028759649598</v>
       </c>
       <c r="E10" t="n">
-        <v>10.17310674809873</v>
+        <v>9.96612659652765</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520660114209097</v>
+        <v>0.7520246865693914</v>
       </c>
       <c r="G10" t="n">
-        <v>27.98754800580021</v>
+        <v>27.23774796961607</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59503652536184</v>
+        <v>34.59313558219199</v>
       </c>
       <c r="I10" t="n">
-        <v>3.944648085577497</v>
+        <v>3.96794748114803</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700412571380685</v>
+        <v>4.700154291058696</v>
       </c>
       <c r="K10" t="n">
-        <v>16.03835466476334</v>
+        <v>17.02283463323858</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17248683996949</v>
+        <v>43.19238904311898</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86871732592334</v>
+        <v>99.86794557761996</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.51015619065925</v>
+        <v>80.56826918288539</v>
       </c>
       <c r="C11" t="n">
-        <v>38.81792679800276</v>
+        <v>37.85813564531278</v>
       </c>
       <c r="D11" t="n">
-        <v>1.700170254162501</v>
+        <v>1.653479139546643</v>
       </c>
       <c r="E11" t="n">
-        <v>10.11060859608435</v>
+        <v>9.914650350251391</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530783696376004</v>
+        <v>0.7530548971779184</v>
       </c>
       <c r="G11" t="n">
-        <v>26.30632250080339</v>
+        <v>25.5888137219732</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64160500332962</v>
+        <v>34.64052527018423</v>
       </c>
       <c r="I11" t="n">
-        <v>3.291631656406784</v>
+        <v>3.311152696390009</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706739810235002</v>
+        <v>4.706593107361989</v>
       </c>
       <c r="K11" t="n">
-        <v>18.48984380934075</v>
+        <v>19.43173081711462</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58265583472377</v>
+        <v>42.59991277420738</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89042644206728</v>
+        <v>99.88977923663478</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.01747005091789</v>
+        <v>78.09785035084134</v>
       </c>
       <c r="C12" t="n">
-        <v>36.83466464433633</v>
+        <v>35.89946159584817</v>
       </c>
       <c r="D12" t="n">
-        <v>1.590827613283254</v>
+        <v>1.545365812566099</v>
       </c>
       <c r="E12" t="n">
-        <v>9.918068142571549</v>
+        <v>9.726801943326526</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539507956638327</v>
+        <v>0.7539428216768017</v>
       </c>
       <c r="G12" t="n">
-        <v>24.61449030516489</v>
+        <v>23.91567995281875</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6817366005363</v>
+        <v>34.68136979713287</v>
       </c>
       <c r="I12" t="n">
-        <v>2.746204120799121</v>
+        <v>2.762547387840288</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712192472898954</v>
+        <v>4.71214263548001</v>
       </c>
       <c r="K12" t="n">
-        <v>20.9825299490821</v>
+        <v>21.90214964915866</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0913711939036</v>
+        <v>42.10641229120456</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90856578732203</v>
+        <v>99.90802353621139</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.46759601349432</v>
+        <v>75.59130427719552</v>
       </c>
       <c r="C13" t="n">
-        <v>34.70888005825982</v>
+        <v>33.81893159394239</v>
       </c>
       <c r="D13" t="n">
-        <v>1.480010876253675</v>
+        <v>1.436742852185298</v>
       </c>
       <c r="E13" t="n">
-        <v>9.608975594270547</v>
+        <v>9.427187123990143</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547036818786796</v>
+        <v>0.754708973625835</v>
       </c>
       <c r="G13" t="n">
-        <v>22.89984977687095</v>
+        <v>22.23465922952393</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71636936641925</v>
+        <v>34.7166127867884</v>
       </c>
       <c r="I13" t="n">
-        <v>2.290788706059457</v>
+        <v>2.304462225920444</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716898011741747</v>
+        <v>4.716931085161468</v>
       </c>
       <c r="K13" t="n">
-        <v>23.53240398650568</v>
+        <v>24.40869572280449</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68243250743452</v>
+        <v>41.69563525581312</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92371655220002</v>
+        <v>99.92326257255999</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.437611887568</v>
+        <v>82.78058705397785</v>
       </c>
       <c r="C14" t="n">
-        <v>39.07772620972062</v>
+        <v>38.23425527193372</v>
       </c>
       <c r="D14" t="n">
-        <v>1.481730354994126</v>
+        <v>1.438524698119448</v>
       </c>
       <c r="E14" t="n">
-        <v>12.03209502822004</v>
+        <v>11.88873472132067</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555804976893951</v>
+        <v>0.7556449623548385</v>
       </c>
       <c r="G14" t="n">
-        <v>24.8537208866919</v>
+        <v>24.19876894563695</v>
       </c>
       <c r="H14" t="n">
-        <v>36.68396892550118</v>
+        <v>36.69620259953974</v>
       </c>
       <c r="I14" t="n">
-        <v>2.908138083912639</v>
+        <v>3.079930112288471</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722378110558718</v>
+        <v>4.722781014717739</v>
       </c>
       <c r="K14" t="n">
-        <v>16.56238811243201</v>
+        <v>17.21941294602214</v>
       </c>
       <c r="L14" t="n">
-        <v>44.26306023365569</v>
+        <v>44.44379461138485</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90317455580831</v>
+        <v>99.8974628293407</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.61914846149151</v>
+        <v>81.94502158289339</v>
       </c>
       <c r="C15" t="n">
-        <v>38.70857140872907</v>
+        <v>37.86079904807805</v>
       </c>
       <c r="D15" t="n">
-        <v>1.451541072769157</v>
+        <v>1.406458613631126</v>
       </c>
       <c r="E15" t="n">
-        <v>12.19125237769215</v>
+        <v>12.06502920043881</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563199963494672</v>
+        <v>0.7564347079909702</v>
       </c>
       <c r="G15" t="n">
-        <v>24.34734265690129</v>
+        <v>23.67244590359295</v>
       </c>
       <c r="H15" t="n">
-        <v>36.71987210980714</v>
+        <v>36.74764537130174</v>
       </c>
       <c r="I15" t="n">
-        <v>2.425820270788142</v>
+        <v>2.569290860994216</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726999977184168</v>
+        <v>4.727716924943564</v>
       </c>
       <c r="K15" t="n">
-        <v>17.38085153850849</v>
+        <v>18.0549784171066</v>
       </c>
       <c r="L15" t="n">
-        <v>43.82979543932042</v>
+        <v>43.9986689205851</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91921838655799</v>
+        <v>99.91444638576976</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.14799131513185</v>
+        <v>79.28631135511445</v>
       </c>
       <c r="C16" t="n">
-        <v>36.61221843940633</v>
+        <v>35.59850415079077</v>
       </c>
       <c r="D16" t="n">
-        <v>1.358264144599618</v>
+        <v>1.306962752006983</v>
       </c>
       <c r="E16" t="n">
-        <v>11.74503793399291</v>
+        <v>11.56869093297223</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756956402464882</v>
+        <v>0.7571162225053181</v>
       </c>
       <c r="G16" t="n">
-        <v>22.78276734123738</v>
+        <v>21.9978069351216</v>
       </c>
       <c r="H16" t="n">
-        <v>36.75077007796973</v>
+        <v>36.78075338898533</v>
       </c>
       <c r="I16" t="n">
-        <v>2.023217899461831</v>
+        <v>2.143004732864749</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730977515405511</v>
+        <v>4.731976390658238</v>
       </c>
       <c r="K16" t="n">
-        <v>19.85200868486814</v>
+        <v>20.71368864488556</v>
       </c>
       <c r="L16" t="n">
-        <v>43.46838897931477</v>
+        <v>43.61643801374048</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93261610358923</v>
+        <v>99.9286308094168</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.90344456761855</v>
+        <v>81.17124731231422</v>
       </c>
       <c r="C17" t="n">
-        <v>37.89104679722961</v>
+        <v>36.95081516047325</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3593744967042</v>
+        <v>1.308120575233527</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54654567413055</v>
+        <v>12.41941513297462</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575751982550055</v>
+        <v>0.7577869430337061</v>
       </c>
       <c r="G17" t="n">
-        <v>23.25852655453439</v>
+        <v>22.49822681016447</v>
       </c>
       <c r="H17" t="n">
-        <v>37.23794783698717</v>
+        <v>37.29426930577443</v>
       </c>
       <c r="I17" t="n">
-        <v>2.00862981791345</v>
+        <v>2.157260151172806</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734844989093783</v>
+        <v>4.736168393960662</v>
       </c>
       <c r="K17" t="n">
-        <v>18.09655543238146</v>
+        <v>18.82875268768577</v>
       </c>
       <c r="L17" t="n">
-        <v>43.94549813215923</v>
+        <v>44.14858712681418</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9331003617703</v>
+        <v>99.92815497497321</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.49863393111188</v>
+        <v>78.58189755984033</v>
       </c>
       <c r="C18" t="n">
-        <v>35.79618765071658</v>
+        <v>34.69381917437308</v>
       </c>
       <c r="D18" t="n">
-        <v>1.272306011235046</v>
+        <v>1.215545496887185</v>
       </c>
       <c r="E18" t="n">
-        <v>12.02210665475387</v>
+        <v>11.84034708008805</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581072677971598</v>
+        <v>0.7583652466809204</v>
       </c>
       <c r="G18" t="n">
-        <v>21.76880853624198</v>
+        <v>20.90603787205155</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26410125106676</v>
+        <v>37.32273035562226</v>
       </c>
       <c r="I18" t="n">
-        <v>1.675033786284826</v>
+        <v>1.799088716754603</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738170423732247</v>
+        <v>4.739782791755752</v>
       </c>
       <c r="K18" t="n">
-        <v>20.5013660688881</v>
+        <v>21.41810244015969</v>
       </c>
       <c r="L18" t="n">
-        <v>43.64665100767549</v>
+        <v>43.82815449237909</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94420472728018</v>
+        <v>99.94007610691185</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.54157718162689</v>
+        <v>77.53850591724384</v>
       </c>
       <c r="C19" t="n">
-        <v>35.09403250892106</v>
+        <v>33.91626924035833</v>
       </c>
       <c r="D19" t="n">
-        <v>1.238191700945056</v>
+        <v>1.178528999219764</v>
       </c>
       <c r="E19" t="n">
-        <v>11.93300520172494</v>
+        <v>11.73150960830664</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585575420431908</v>
+        <v>0.7588576589022835</v>
       </c>
       <c r="G19" t="n">
-        <v>21.18512199975548</v>
+        <v>20.26939506097819</v>
       </c>
       <c r="H19" t="n">
-        <v>37.28623408873708</v>
+        <v>37.34696428332686</v>
       </c>
       <c r="I19" t="n">
-        <v>1.399482010651199</v>
+        <v>1.510389938370827</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740984637769941</v>
+        <v>4.742860368139271</v>
       </c>
       <c r="K19" t="n">
-        <v>21.45842281837311</v>
+        <v>22.46149408275616</v>
       </c>
       <c r="L19" t="n">
-        <v>43.40092296309593</v>
+        <v>43.57192301464334</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95337829039009</v>
+        <v>99.94968633775784</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.96435201330043</v>
+        <v>74.8605239820305</v>
       </c>
       <c r="C20" t="n">
-        <v>32.73202377762154</v>
+        <v>31.47008577252283</v>
       </c>
       <c r="D20" t="n">
-        <v>1.145895666680294</v>
+        <v>1.08401497463118</v>
       </c>
       <c r="E20" t="n">
-        <v>11.23797921118843</v>
+        <v>11.00057638119822</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589459300567866</v>
+        <v>0.7592831960800803</v>
       </c>
       <c r="G20" t="n">
-        <v>19.60596204859427</v>
+        <v>18.64385839242162</v>
       </c>
       <c r="H20" t="n">
-        <v>37.30532496265178</v>
+        <v>37.36790697474463</v>
       </c>
       <c r="I20" t="n">
-        <v>1.166832131273943</v>
+        <v>1.259364087454278</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743412062854914</v>
+        <v>4.745519975500502</v>
       </c>
       <c r="K20" t="n">
-        <v>24.03564798669958</v>
+        <v>25.13947601796948</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19345373538302</v>
+        <v>43.34848293344182</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96112549970414</v>
+        <v>99.95804472393414</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.00397553253342</v>
+        <v>81.21665314363564</v>
       </c>
       <c r="C21" t="n">
-        <v>36.52039566175605</v>
+        <v>35.44100347373929</v>
       </c>
       <c r="D21" t="n">
-        <v>1.146655668951619</v>
+        <v>1.084804948998017</v>
       </c>
       <c r="E21" t="n">
-        <v>13.26846032621849</v>
+        <v>13.13463507076838</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759449292315174</v>
+        <v>0.7598365226264013</v>
       </c>
       <c r="G21" t="n">
-        <v>21.37005211143211</v>
+        <v>20.48755451208516</v>
       </c>
       <c r="H21" t="n">
-        <v>39.08115392668877</v>
+        <v>39.22524821810998</v>
       </c>
       <c r="I21" t="n">
-        <v>1.63164612995742</v>
+        <v>1.775595604632703</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746558076969835</v>
+        <v>4.748978266415008</v>
       </c>
       <c r="K21" t="n">
-        <v>17.99602446746658</v>
+        <v>18.78334685636436</v>
       </c>
       <c r="L21" t="n">
-        <v>45.42922771489483</v>
+        <v>45.71650625042452</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94564784411746</v>
+        <v>99.94085658052816</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_54_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_54_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.27959449086548</v>
+        <v>43.88370442331976</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0938855455669</v>
+        <v>94.08704106125893</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96871288811518</v>
+        <v>81.44239189697565</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90896296633276</v>
+        <v>43.19794745253121</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228595177605697</v>
+        <v>2.178586493484834</v>
       </c>
       <c r="E3" t="n">
-        <v>5.691848593596602</v>
+        <v>4.143205692712715</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428650592018989</v>
+        <v>0.7376086131427063</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96689678444901</v>
+        <v>32.76957183950105</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17179272328735</v>
+        <v>33.92999620456449</v>
       </c>
       <c r="I3" t="n">
-        <v>6.523807929962755</v>
+        <v>3.073369221427943</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642906620011868</v>
+        <v>4.610053832141914</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03128711188482</v>
+        <v>18.55760810302434</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8255644404346</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7658145186522</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.95403958337575</v>
+        <v>88.52628538769021</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52161674483083</v>
+        <v>42.77746539894334</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179151456348896</v>
+        <v>2.184324279456574</v>
       </c>
       <c r="E4" t="n">
-        <v>6.473545670137641</v>
+        <v>6.51354560016473</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444164630777247</v>
+        <v>0.7395512674122435</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21330555646603</v>
+        <v>33.45270810143179</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24315730157533</v>
+        <v>34.01935830096321</v>
       </c>
       <c r="I4" t="n">
-        <v>5.447860241534332</v>
+        <v>6.994602416935134</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652602894235779</v>
+        <v>4.622195421326522</v>
       </c>
       <c r="K4" t="n">
-        <v>13.04596041662425</v>
+        <v>11.4737146123098</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25120595160151</v>
+        <v>45.51627902255201</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8187831130566</v>
+        <v>99.76745903380515</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.66490875164759</v>
+        <v>87.39376472223044</v>
       </c>
       <c r="C5" t="n">
-        <v>42.07793557007077</v>
+        <v>42.72908114091324</v>
       </c>
       <c r="D5" t="n">
-        <v>2.115788995741986</v>
+        <v>2.130371131415514</v>
       </c>
       <c r="E5" t="n">
-        <v>7.043302799897259</v>
+        <v>7.326297170694661</v>
       </c>
       <c r="F5" t="n">
-        <v>0.74573382267966</v>
+        <v>0.7411991071519145</v>
       </c>
       <c r="G5" t="n">
-        <v>32.24757334046264</v>
+        <v>32.62642102970636</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30375584326436</v>
+        <v>34.09515892898807</v>
       </c>
       <c r="I5" t="n">
-        <v>4.547917557853802</v>
+        <v>5.84182293457446</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660836391747875</v>
+        <v>4.632494419699466</v>
       </c>
       <c r="K5" t="n">
-        <v>14.33509124835243</v>
+        <v>12.60623527776955</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43564373042305</v>
+        <v>44.47038906973567</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84867054884626</v>
+        <v>99.80570548841847</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.17649388579494</v>
+        <v>86.04240405364155</v>
       </c>
       <c r="C6" t="n">
-        <v>41.29563930929751</v>
+        <v>42.28429206684822</v>
       </c>
       <c r="D6" t="n">
-        <v>2.042800097690808</v>
+        <v>2.065857367818222</v>
       </c>
       <c r="E6" t="n">
-        <v>7.432932856885212</v>
+        <v>7.917333217616315</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468546929865996</v>
+        <v>0.7425996231589442</v>
       </c>
       <c r="G6" t="n">
-        <v>31.13512080021322</v>
+        <v>31.63839918586095</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35531587738357</v>
+        <v>34.15958266531144</v>
       </c>
       <c r="I6" t="n">
-        <v>3.795627729469295</v>
+        <v>4.87738434913227</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667841831166247</v>
+        <v>4.641247644743402</v>
       </c>
       <c r="K6" t="n">
-        <v>15.82350611420505</v>
+        <v>13.95759594635845</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75452353322373</v>
+        <v>43.59583912749959</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87366895672629</v>
+        <v>99.83772714070625</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.39209056447311</v>
+        <v>84.58790988945013</v>
       </c>
       <c r="C7" t="n">
-        <v>40.10047564443585</v>
+        <v>41.58710972319803</v>
       </c>
       <c r="D7" t="n">
-        <v>1.955543789262939</v>
+        <v>1.996862945383365</v>
       </c>
       <c r="E7" t="n">
-        <v>7.643288017954902</v>
+        <v>8.331415505176182</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478116398168456</v>
+        <v>0.7437909394185243</v>
       </c>
       <c r="G7" t="n">
-        <v>29.80521303951095</v>
+        <v>30.5817564995862</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39933543157489</v>
+        <v>34.21438321325212</v>
       </c>
       <c r="I7" t="n">
-        <v>3.167075897497298</v>
+        <v>4.071007415267951</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673822748855285</v>
+        <v>4.648693371365776</v>
       </c>
       <c r="K7" t="n">
-        <v>17.60790943552689</v>
+        <v>15.41209011054989</v>
       </c>
       <c r="L7" t="n">
-        <v>42.1861808164409</v>
+        <v>42.86531726766506</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89456589640363</v>
+        <v>99.86451710141299</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.4180395505264</v>
+        <v>82.96190815938289</v>
       </c>
       <c r="C8" t="n">
-        <v>42.47365304477685</v>
+        <v>40.59324185606204</v>
       </c>
       <c r="D8" t="n">
-        <v>1.959789747270413</v>
+        <v>1.920113310501617</v>
       </c>
       <c r="E8" t="n">
-        <v>9.527451407844318</v>
+        <v>8.577386141047528</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494353195511457</v>
+        <v>0.744806168208119</v>
       </c>
       <c r="G8" t="n">
-        <v>30.32919713210622</v>
+        <v>29.40634350951985</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47402469935269</v>
+        <v>34.26108373757348</v>
       </c>
       <c r="I8" t="n">
-        <v>5.694170497206941</v>
+        <v>3.397136741231553</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68397074719466</v>
+        <v>4.655038551300743</v>
       </c>
       <c r="K8" t="n">
-        <v>12.5819604494736</v>
+        <v>17.03809184061711</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75499204364247</v>
+        <v>42.25558276400785</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81060553789293</v>
+        <v>99.88691646068702</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.28181506397294</v>
+        <v>81.2029823587187</v>
       </c>
       <c r="C9" t="n">
-        <v>41.22050613371963</v>
+        <v>39.36154787600618</v>
       </c>
       <c r="D9" t="n">
-        <v>1.863127926977934</v>
+        <v>1.837611893076007</v>
       </c>
       <c r="E9" t="n">
-        <v>9.84985978018233</v>
+        <v>8.681215484428192</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508278731429323</v>
+        <v>0.7456727045744439</v>
       </c>
       <c r="G9" t="n">
-        <v>28.83328390627062</v>
+        <v>28.14284254446171</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53808216457487</v>
+        <v>34.30094441042443</v>
       </c>
       <c r="I9" t="n">
-        <v>4.753959205680934</v>
+        <v>2.834240918163639</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692674207143327</v>
+        <v>4.660454403590275</v>
       </c>
       <c r="K9" t="n">
-        <v>14.71818493602703</v>
+        <v>18.79701764128131</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90313752755314</v>
+        <v>41.74706957323385</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84182859729981</v>
+        <v>99.90563509052134</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.97716536676143</v>
+        <v>85.87658734418243</v>
       </c>
       <c r="C10" t="n">
-        <v>39.6527219012624</v>
+        <v>42.40630081104483</v>
       </c>
       <c r="D10" t="n">
-        <v>1.760028759649598</v>
+        <v>1.839874190240165</v>
       </c>
       <c r="E10" t="n">
-        <v>9.96612659652765</v>
+        <v>10.45753630720452</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520246865693914</v>
+        <v>0.746590707582209</v>
       </c>
       <c r="G10" t="n">
-        <v>27.23774796961607</v>
+        <v>29.41450630669763</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59313558219199</v>
+        <v>35.58018945597726</v>
       </c>
       <c r="I10" t="n">
-        <v>3.96794748114803</v>
+        <v>3.171698454091833</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700154291058696</v>
+        <v>4.666191922388807</v>
       </c>
       <c r="K10" t="n">
-        <v>17.02283463323858</v>
+        <v>14.12341265581757</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19238904311898</v>
+        <v>43.36469324798425</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86794557761996</v>
+        <v>99.89440671484665</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.56826918288539</v>
+        <v>85.65373061531841</v>
       </c>
       <c r="C11" t="n">
-        <v>37.85813564531278</v>
+        <v>42.64253005340011</v>
       </c>
       <c r="D11" t="n">
-        <v>1.653479139546643</v>
+        <v>1.828456749613328</v>
       </c>
       <c r="E11" t="n">
-        <v>9.914650350251391</v>
+        <v>10.85719404569978</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530548971779184</v>
+        <v>0.7473628201822156</v>
       </c>
       <c r="G11" t="n">
-        <v>25.5888137219732</v>
+        <v>29.25361668508977</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64052527018423</v>
+        <v>35.63862965680647</v>
       </c>
       <c r="I11" t="n">
-        <v>3.311152696390009</v>
+        <v>2.657453031788005</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706593107361989</v>
+        <v>4.671017626138847</v>
       </c>
       <c r="K11" t="n">
-        <v>19.43173081711462</v>
+        <v>14.3462693846816</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59991277420738</v>
+        <v>42.92271030944691</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88977923663478</v>
+        <v>99.91150974752861</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.09785035084134</v>
+        <v>83.79239587292871</v>
       </c>
       <c r="C12" t="n">
-        <v>35.89946159584817</v>
+        <v>41.19438625705484</v>
       </c>
       <c r="D12" t="n">
-        <v>1.545365812566099</v>
+        <v>1.748847457785383</v>
       </c>
       <c r="E12" t="n">
-        <v>9.726801943326526</v>
+        <v>10.75389814217327</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539428216768017</v>
+        <v>0.7480218009558303</v>
       </c>
       <c r="G12" t="n">
-        <v>23.91567995281875</v>
+        <v>27.97994165383805</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68136979713287</v>
+        <v>35.67005371364687</v>
       </c>
       <c r="I12" t="n">
-        <v>2.762547387840288</v>
+        <v>2.216496848555363</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71214263548001</v>
+        <v>4.67513625597394</v>
       </c>
       <c r="K12" t="n">
-        <v>21.90214964915866</v>
+        <v>16.2076041270713</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10641229120456</v>
+        <v>42.52419147610198</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90802353621139</v>
+        <v>99.92618186022811</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.59130427719552</v>
+        <v>84.97505824484961</v>
       </c>
       <c r="C13" t="n">
-        <v>33.81893159394239</v>
+        <v>42.1651342221863</v>
       </c>
       <c r="D13" t="n">
-        <v>1.436742852185298</v>
+        <v>1.750291119416371</v>
       </c>
       <c r="E13" t="n">
-        <v>9.427187123990143</v>
+        <v>11.40573950155744</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754708973625835</v>
+        <v>0.7486392878431944</v>
       </c>
       <c r="G13" t="n">
-        <v>22.23465922952393</v>
+        <v>28.29527134366289</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7166127867884</v>
+        <v>35.99173153845017</v>
       </c>
       <c r="I13" t="n">
-        <v>2.304462225920444</v>
+        <v>2.104389904899582</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716931085161468</v>
+        <v>4.678995549019966</v>
       </c>
       <c r="K13" t="n">
-        <v>24.40869572280449</v>
+        <v>15.02494175515038</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69563525581312</v>
+        <v>42.73983555005542</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92326257255999</v>
+        <v>99.92991152739209</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.78058705397785</v>
+        <v>83.13199382723596</v>
       </c>
       <c r="C14" t="n">
-        <v>38.23425527193372</v>
+        <v>40.64915321054674</v>
       </c>
       <c r="D14" t="n">
-        <v>1.438524698119448</v>
+        <v>1.673644127740017</v>
       </c>
       <c r="E14" t="n">
-        <v>11.88873472132067</v>
+        <v>11.1987528449187</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556449623548385</v>
+        <v>0.7491660731025117</v>
       </c>
       <c r="G14" t="n">
-        <v>24.19876894563695</v>
+        <v>27.05619322511479</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69620259953974</v>
+        <v>36.01705737151777</v>
       </c>
       <c r="I14" t="n">
-        <v>3.079930112288471</v>
+        <v>1.754892227951485</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722781014717739</v>
+        <v>4.682287956890699</v>
       </c>
       <c r="K14" t="n">
-        <v>17.21941294602214</v>
+        <v>16.86800617276404</v>
       </c>
       <c r="L14" t="n">
-        <v>44.44379461138485</v>
+        <v>42.42438534155312</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8974628293407</v>
+        <v>99.94154472486389</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.94502158289339</v>
+        <v>82.33582589152294</v>
       </c>
       <c r="C15" t="n">
-        <v>37.86079904807805</v>
+        <v>40.11665807979445</v>
       </c>
       <c r="D15" t="n">
-        <v>1.406458613631126</v>
+        <v>1.640827233018384</v>
       </c>
       <c r="E15" t="n">
-        <v>12.06502920043881</v>
+        <v>11.22444586819415</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564347079909702</v>
+        <v>0.7496124267647305</v>
       </c>
       <c r="G15" t="n">
-        <v>23.67244590359295</v>
+        <v>26.52567408432484</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74764537130174</v>
+        <v>36.03851635910051</v>
       </c>
       <c r="I15" t="n">
-        <v>2.569290860994216</v>
+        <v>1.471672252840744</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727716924943564</v>
+        <v>4.685077667279566</v>
       </c>
       <c r="K15" t="n">
-        <v>18.0549784171066</v>
+        <v>17.66417410847707</v>
       </c>
       <c r="L15" t="n">
-        <v>43.9986689205851</v>
+        <v>42.17014128000847</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91444638576976</v>
+        <v>99.95097346828</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.28631135511445</v>
+        <v>80.1713961804011</v>
       </c>
       <c r="C16" t="n">
-        <v>35.59850415079077</v>
+        <v>38.18052882518595</v>
       </c>
       <c r="D16" t="n">
-        <v>1.306962752006983</v>
+        <v>1.551459156789852</v>
       </c>
       <c r="E16" t="n">
-        <v>11.56869093297223</v>
+        <v>10.81760674534259</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7571162225053181</v>
+        <v>0.7499948527875344</v>
       </c>
       <c r="G16" t="n">
-        <v>21.9978069351216</v>
+        <v>25.08094643970841</v>
       </c>
       <c r="H16" t="n">
-        <v>36.78075338898533</v>
+        <v>36.05690194875575</v>
       </c>
       <c r="I16" t="n">
-        <v>2.143004732864749</v>
+        <v>1.227019207094878</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731976390658238</v>
+        <v>4.68746782992209</v>
       </c>
       <c r="K16" t="n">
-        <v>20.71368864488556</v>
+        <v>19.82860381959889</v>
       </c>
       <c r="L16" t="n">
-        <v>43.61643801374048</v>
+        <v>41.94998757041403</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9286308094168</v>
+        <v>99.95912021519888</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.17124731231422</v>
+        <v>84.67160984694397</v>
       </c>
       <c r="C17" t="n">
-        <v>36.95081516047325</v>
+        <v>41.03223089824063</v>
       </c>
       <c r="D17" t="n">
-        <v>1.308120575233527</v>
+        <v>1.552410554125868</v>
       </c>
       <c r="E17" t="n">
-        <v>12.41941513297462</v>
+        <v>12.37102803675734</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577869430337061</v>
+        <v>0.7504547702154896</v>
       </c>
       <c r="G17" t="n">
-        <v>22.49822681016447</v>
+        <v>26.38349962729206</v>
       </c>
       <c r="H17" t="n">
-        <v>37.29426930577443</v>
+        <v>37.36618589350169</v>
       </c>
       <c r="I17" t="n">
-        <v>2.157260151172806</v>
+        <v>1.557688651204707</v>
       </c>
       <c r="J17" t="n">
-        <v>4.736168393960662</v>
+        <v>4.69034231384681</v>
       </c>
       <c r="K17" t="n">
-        <v>18.82875268768577</v>
+        <v>15.32839015305602</v>
       </c>
       <c r="L17" t="n">
-        <v>44.14858712681418</v>
+        <v>43.58748781473074</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92815497497321</v>
+        <v>99.9481088660274</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.58189755984033</v>
+        <v>86.28744875840968</v>
       </c>
       <c r="C18" t="n">
-        <v>34.69381917437308</v>
+        <v>41.80731489827259</v>
       </c>
       <c r="D18" t="n">
-        <v>1.215545496887185</v>
+        <v>1.553818392803411</v>
       </c>
       <c r="E18" t="n">
-        <v>11.84034708008805</v>
+        <v>13.01306785874698</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583652466809204</v>
+        <v>0.7511353371238035</v>
       </c>
       <c r="G18" t="n">
-        <v>20.90603787205155</v>
+        <v>26.527207220169</v>
       </c>
       <c r="H18" t="n">
-        <v>37.32273035562226</v>
+        <v>37.40007226563004</v>
       </c>
       <c r="I18" t="n">
-        <v>1.799088716754603</v>
+        <v>2.347551826912684</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739782791755752</v>
+        <v>4.694595857023772</v>
       </c>
       <c r="K18" t="n">
-        <v>21.41810244015969</v>
+        <v>13.71255124159028</v>
       </c>
       <c r="L18" t="n">
-        <v>43.82815449237909</v>
+        <v>44.40195303262781</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94007610691185</v>
+        <v>99.9218191724907</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.53850591724384</v>
+        <v>83.92253634860367</v>
       </c>
       <c r="C19" t="n">
-        <v>33.91626924035833</v>
+        <v>39.80636526388612</v>
       </c>
       <c r="D19" t="n">
-        <v>1.178528999219764</v>
+        <v>1.465536892227624</v>
       </c>
       <c r="E19" t="n">
-        <v>11.73150960830664</v>
+        <v>12.60002185850852</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588576589022835</v>
+        <v>0.7517194407054898</v>
       </c>
       <c r="G19" t="n">
-        <v>20.26939506097819</v>
+        <v>25.02004160137609</v>
       </c>
       <c r="H19" t="n">
-        <v>37.34696428332686</v>
+        <v>37.42915559467342</v>
       </c>
       <c r="I19" t="n">
-        <v>1.510389938370827</v>
+        <v>1.957814456703218</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742860368139271</v>
+        <v>4.698246504409312</v>
       </c>
       <c r="K19" t="n">
-        <v>22.46149408275616</v>
+        <v>16.07746365139634</v>
       </c>
       <c r="L19" t="n">
-        <v>43.57192301464334</v>
+        <v>44.05096131174772</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94968633775784</v>
+        <v>99.93479022703016</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.8605239820305</v>
+        <v>81.42513708610952</v>
       </c>
       <c r="C20" t="n">
-        <v>31.47008577252283</v>
+        <v>37.61183920486567</v>
       </c>
       <c r="D20" t="n">
-        <v>1.08401497463118</v>
+        <v>1.372812381023577</v>
       </c>
       <c r="E20" t="n">
-        <v>11.00057638119822</v>
+        <v>12.07491895404351</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592831960800803</v>
+        <v>0.7522218486236318</v>
       </c>
       <c r="G20" t="n">
-        <v>18.64385839242162</v>
+        <v>23.43702370527512</v>
       </c>
       <c r="H20" t="n">
-        <v>37.36790697474463</v>
+        <v>37.45417118309893</v>
       </c>
       <c r="I20" t="n">
-        <v>1.259364087454278</v>
+        <v>1.632602460147039</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745519975500502</v>
+        <v>4.7013865538977</v>
       </c>
       <c r="K20" t="n">
-        <v>25.13947601796948</v>
+        <v>18.5748629138905</v>
       </c>
       <c r="L20" t="n">
-        <v>43.34848293344182</v>
+        <v>43.75891414633542</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95804472393414</v>
+        <v>99.94561626509159</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.21665314363564</v>
+        <v>78.99906179432888</v>
       </c>
       <c r="C21" t="n">
-        <v>35.44100347373929</v>
+        <v>35.43765193887229</v>
       </c>
       <c r="D21" t="n">
-        <v>1.084804948998017</v>
+        <v>1.283253033426818</v>
       </c>
       <c r="E21" t="n">
-        <v>13.13463507076838</v>
+        <v>11.51405761624552</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598365226264013</v>
+        <v>0.7526539158627045</v>
       </c>
       <c r="G21" t="n">
-        <v>20.48755451208516</v>
+        <v>21.9080423370497</v>
       </c>
       <c r="H21" t="n">
-        <v>39.22524821810998</v>
+        <v>37.47568441136323</v>
       </c>
       <c r="I21" t="n">
-        <v>1.775595604632703</v>
+        <v>1.361283506239002</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748978266415008</v>
+        <v>4.704086974141903</v>
       </c>
       <c r="K21" t="n">
-        <v>18.78334685636436</v>
+        <v>21.00093820567113</v>
       </c>
       <c r="L21" t="n">
-        <v>45.71650625042452</v>
+        <v>43.51605978711916</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94085658052816</v>
+        <v>99.95464993166259</v>
       </c>
     </row>
   </sheetData>
